--- a/data/trans_orig/P78A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243048</t>
+          <t>239596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>280496</t>
+          <t>281518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334538</t>
+          <t>333757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>362591</t>
+          <t>361093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>584653</t>
+          <t>583942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>636222</t>
+          <t>634706</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58806</t>
+          <t>62258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56640</t>
+          <t>58138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84693</t>
+          <t>85474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84863</t>
+          <t>86379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136432</t>
+          <t>137143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>291370</t>
+          <t>289090</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>333306</t>
+          <t>333765</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>410750</t>
+          <t>412635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>450768</t>
+          <t>451355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713312</t>
+          <t>717310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>773691</t>
+          <t>776595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52206</t>
+          <t>51747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94142</t>
+          <t>96422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>110535</t>
+          <t>109948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150553</t>
+          <t>148668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173123</t>
+          <t>170219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233502</t>
+          <t>229504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>260862</t>
+          <t>264294</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>310591</t>
+          <t>311275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>443875</t>
+          <t>444113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>571361</t>
+          <t>571602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>739086</t>
+          <t>737344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>874935</t>
+          <t>881311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40246</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89975</t>
+          <t>86543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43908</t>
+          <t>43667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171394</t>
+          <t>171156</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91170</t>
+          <t>84794</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227019</t>
+          <t>228761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>354377</t>
+          <t>354722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>401126</t>
+          <t>400893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>436275</t>
+          <t>434567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>474808</t>
+          <t>474675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>806696</t>
+          <t>802075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>868548</t>
+          <t>866191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>44353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90869</t>
+          <t>90524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135370</t>
+          <t>135503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173903</t>
+          <t>175611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>186876</t>
+          <t>189233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>248728</t>
+          <t>253349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1202066</t>
+          <t>1194297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1290581</t>
+          <t>1289961</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1683269</t>
+          <t>1685046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1878105</t>
+          <t>1862130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2933330</t>
+          <t>2926382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3136524</t>
+          <t>3123572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192867</t>
+          <t>193487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>281382</t>
+          <t>289151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327875</t>
+          <t>343850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>522711</t>
+          <t>520934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>552904</t>
+          <t>565856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>756098</t>
+          <t>763046</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>265538</t>
+          <t>287207</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>239596</t>
+          <t>265959</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>281518</t>
+          <t>302270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>349465</t>
+          <t>375401</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>333757</t>
+          <t>359052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>361093</t>
+          <t>388754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>615003</t>
+          <t>662609</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>583942</t>
+          <t>632828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>634706</t>
+          <t>683418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36316</t>
+          <t>34697</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62258</t>
+          <t>55945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>69766</t>
+          <t>80463</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58138</t>
+          <t>67110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85474</t>
+          <t>96812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>106082</t>
+          <t>115159</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86379</t>
+          <t>94350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137143</t>
+          <t>144940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>301854</t>
+          <t>321904</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>301854</t>
+          <t>321904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>301854</t>
+          <t>321904</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>419231</t>
+          <t>455864</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>419231</t>
+          <t>455864</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>419231</t>
+          <t>455864</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>721085</t>
+          <t>777768</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>721085</t>
+          <t>777768</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>721085</t>
+          <t>777768</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>315139</t>
+          <t>350658</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>289090</t>
+          <t>328379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>333765</t>
+          <t>370051</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>433235</t>
+          <t>482210</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>412635</t>
+          <t>458112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>451355</t>
+          <t>503369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>748373</t>
+          <t>832868</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>717310</t>
+          <t>798445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>776595</t>
+          <t>860035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70373</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51747</t>
+          <t>51012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96422</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>128068</t>
+          <t>144689</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109948</t>
+          <t>123530</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>148668</t>
+          <t>168787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>198441</t>
+          <t>215094</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170219</t>
+          <t>187927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>229504</t>
+          <t>249517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>385512</t>
+          <t>421063</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>385512</t>
+          <t>421063</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>385512</t>
+          <t>421063</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>561303</t>
+          <t>626899</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>561303</t>
+          <t>626899</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>561303</t>
+          <t>626899</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>946814</t>
+          <t>1047962</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>946814</t>
+          <t>1047962</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>946814</t>
+          <t>1047962</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>289698</t>
+          <t>327557</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>264294</t>
+          <t>305150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>311275</t>
+          <t>347028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>508021</t>
+          <t>351947</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>444113</t>
+          <t>331957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>571602</t>
+          <t>373049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>797719</t>
+          <t>679503</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>737344</t>
+          <t>650281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>881311</t>
+          <t>708687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61139</t>
+          <t>56975</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>37504</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86543</t>
+          <t>79382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>107248</t>
+          <t>126104</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>105002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171156</t>
+          <t>146094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>168386</t>
+          <t>183079</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84794</t>
+          <t>153895</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>228761</t>
+          <t>212301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>350837</t>
+          <t>384532</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>350837</t>
+          <t>384532</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>350837</t>
+          <t>384532</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>615269</t>
+          <t>478051</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>615269</t>
+          <t>478051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>615269</t>
+          <t>478051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>966105</t>
+          <t>862582</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>966105</t>
+          <t>862582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>966105</t>
+          <t>862582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>381495</t>
+          <t>396056</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>354722</t>
+          <t>372320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>400893</t>
+          <t>415913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>456094</t>
+          <t>495266</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>434567</t>
+          <t>472544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>474675</t>
+          <t>517313</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>837589</t>
+          <t>891322</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>802075</t>
+          <t>861149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>866191</t>
+          <t>922385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>63751</t>
+          <t>66875</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44353</t>
+          <t>47018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90524</t>
+          <t>90611</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>154084</t>
+          <t>172597</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135503</t>
+          <t>150550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175611</t>
+          <t>195319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>217835</t>
+          <t>239472</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189233</t>
+          <t>208409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253349</t>
+          <t>269645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>445246</t>
+          <t>462931</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>445246</t>
+          <t>462931</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>445246</t>
+          <t>462931</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>610178</t>
+          <t>667863</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>610178</t>
+          <t>667863</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>610178</t>
+          <t>667863</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1055424</t>
+          <t>1130794</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1055424</t>
+          <t>1130794</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1055424</t>
+          <t>1130794</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1251869</t>
+          <t>1361478</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1194297</t>
+          <t>1317882</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1289961</t>
+          <t>1400476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1746814</t>
+          <t>1704824</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1685046</t>
+          <t>1656945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1862130</t>
+          <t>1741603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2998684</t>
+          <t>3066302</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2926382</t>
+          <t>3006077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3123572</t>
+          <t>3123037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>231579</t>
+          <t>228952</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193487</t>
+          <t>189954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>289151</t>
+          <t>272548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>459166</t>
+          <t>523852</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>343850</t>
+          <t>487073</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>520934</t>
+          <t>571731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>690744</t>
+          <t>752804</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>565856</t>
+          <t>696069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>763046</t>
+          <t>813029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1483448</t>
+          <t>1590430</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1483448</t>
+          <t>1590430</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1483448</t>
+          <t>1590430</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2205980</t>
+          <t>2228676</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2205980</t>
+          <t>2228676</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2205980</t>
+          <t>2228676</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3689428</t>
+          <t>3819106</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3689428</t>
+          <t>3819106</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3689428</t>
+          <t>3819106</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
